--- a/estoque.xlsx
+++ b/estoque.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d651025d1119fcad/Documentos/0 - Arqs/0 - Saude - Elza e Ze/Forms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{9F421B99-81CC-438B-8CEA-FED494C34511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC83DB4A-1316-48B4-9C38-F8ACB63B35F0}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{9F421B99-81CC-438B-8CEA-FED494C34511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4E24C40-DCAA-4C95-82CC-FF235F0AE235}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1067,7 +1067,7 @@
         <v>9</v>
       </c>
       <c r="E4" s="4">
-        <v>46174</v>
+        <v>46190</v>
       </c>
       <c r="F4" s="5"/>
     </row>
@@ -1085,7 +1085,7 @@
         <v>10</v>
       </c>
       <c r="E5" s="4">
-        <v>46174</v>
+        <v>46193</v>
       </c>
       <c r="F5" s="5"/>
     </row>
@@ -1103,7 +1103,7 @@
         <v>10</v>
       </c>
       <c r="E6" s="4">
-        <v>46174</v>
+        <v>46193</v>
       </c>
       <c r="F6" s="5"/>
     </row>
